--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487700_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487700_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3443</v>
+        <v>4.489</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5857</v>
+        <v>4.7849</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2414</v>
+        <v>-0.2959</v>
       </c>
       <c r="G2" t="n">
         <v>3.718</v>
@@ -610,13 +610,13 @@
         <v>0.3881</v>
       </c>
       <c r="S2" t="n">
-        <v>1.286</v>
+        <v>0.4307</v>
       </c>
       <c r="T2" t="n">
-        <v>1.153</v>
+        <v>0.3522</v>
       </c>
       <c r="U2" t="n">
-        <v>0.133</v>
+        <v>0.0785</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0478</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.264</v>
+        <v>2.7804</v>
       </c>
       <c r="E3" t="n">
-        <v>5.792</v>
+        <v>4.0903</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.528</v>
+        <v>-1.3099</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7561</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7963</v>
+        <v>0.3126</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2465</v>
+        <v>0.5448</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4502</v>
+        <v>-0.2321</v>
       </c>
       <c r="V3" t="n">
         <v>2.4477</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2307</v>
+        <v>2.7128</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2759</v>
+        <v>1.6763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9547</v>
+        <v>1.0365</v>
       </c>
       <c r="G4" t="n">
         <v>1.6793</v>
@@ -766,13 +766,13 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6128</v>
+        <v>-0.1307</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6057</v>
+        <v>-0.2053</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0072</v>
+        <v>0.0746</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9387</v>
+        <v>2.5665</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6501</v>
+        <v>2.2507</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2886</v>
+        <v>0.3158</v>
       </c>
       <c r="G5" t="n">
         <v>0.4444</v>
@@ -844,13 +844,13 @@
         <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.758</v>
+        <v>-0.1301</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8479</v>
+        <v>-0.2473</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09</v>
+        <v>0.1172</v>
       </c>
       <c r="V5" t="n">
         <v>0.894</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3069</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0985</v>
+        <v>0.0799</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2084</v>
+        <v>0.4871</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8882</v>
+        <v>-1.1367</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4119</v>
+        <v>-0.4004</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3002</v>
+        <v>-0.7363</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3759</v>
+        <v>-0.0177</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3048</v>
+        <v>-0.0989</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0711</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5123</v>
+        <v>-1.1191</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7168</v>
+        <v>-0.3015</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.229</v>
+        <v>-0.8175</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>0.225</v>
+        <v>0.3454</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6684</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4435</v>
+        <v>0.2479</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2211</v>
+        <v>-0.0117</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3205</v>
+        <v>-0.3019</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5416</v>
+        <v>0.2902</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1367</v>
+        <v>-0.8882</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4004</v>
+        <v>0.4119</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7363</v>
+        <v>-1.3002</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0177</v>
+        <v>-0.3759</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0989</v>
+        <v>-0.3048</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0711</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1191</v>
+        <v>-0.5123</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3015</v>
+        <v>0.7168</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8175</v>
+        <v>-1.229</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0004</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3028</v>
+        <v>0.268</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3024</v>
+        <v>-0.3617</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.506</v>
+        <v>-2.3143</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3871</v>
+        <v>0.9877</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8932</v>
+        <v>-3.302</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1811</v>
@@ -1078,13 +1078,13 @@
         <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0168</v>
+        <v>0.2086</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7268</v>
+        <v>-0.1262</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7436</v>
+        <v>0.3348</v>
       </c>
       <c r="V8" t="n">
         <v>-2.7298</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3077</v>
+        <v>-2.5436</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1931</v>
+        <v>0.4075</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1146</v>
+        <v>-2.9511</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4844</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.201</v>
+        <v>-0.4368</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8479</v>
+        <v>-0.2473</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.353</v>
+        <v>-0.1895</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8462</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4813</v>
+        <v>-4.7003</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.516</v>
+        <v>-3.5103</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9653</v>
+        <v>-1.1901</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.817</v>
+        <v>-4.2475</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8529</v>
+        <v>0.4811</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9641</v>
+        <v>-4.7286</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9402</v>
+        <v>-1.7249</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6055</v>
+        <v>2.175</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3347</v>
+        <v>-3.9</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8768</v>
+        <v>-2.5225</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2473</v>
+        <v>-1.6939</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6294</v>
+        <v>-0.8286</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9702</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1642</v>
+        <v>-3.1045</v>
       </c>
       <c r="R10" t="n">
-        <v>0.194</v>
+        <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3641</v>
+        <v>-0.2125</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3645</v>
+        <v>-0.1868</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0004</v>
+        <v>-0.0258</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9418</v>
+        <v>1.506</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3009</v>
+        <v>-4.8361</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1109</v>
+        <v>-1.8163</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1901</v>
+        <v>-3.0198</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.2475</v>
+        <v>-4.817</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4811</v>
+        <v>-1.8529</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.7286</v>
+        <v>-2.9641</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7249</v>
+        <v>-1.9402</v>
       </c>
       <c r="K11" t="n">
-        <v>2.175</v>
+        <v>-0.6055</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.9</v>
+        <v>-1.3347</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5225</v>
+        <v>-2.8768</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6939</v>
+        <v>-1.2473</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8286</v>
+        <v>-1.6294</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7463</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1045</v>
+        <v>-1.1642</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8131</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7874</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0258</v>
+        <v>-0.055</v>
       </c>
       <c r="V11" t="n">
-        <v>1.506</v>
+        <v>0.9418</v>
       </c>
       <c r="W11" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.290200000000001</v>
+        <v>-1.2903</v>
       </c>
       <c r="E12" t="n">
-        <v>8.648800000000001</v>
+        <v>8.6488</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.939299999999998</v>
+        <v>-9.9392</v>
       </c>
       <c r="G12" t="n">
         <v>-6.669300000000001</v>
@@ -1390,13 +1390,13 @@
         <v>12.6121</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3028999999999998</v>
+        <v>0.3028</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3139000000000002</v>
+        <v>0.3139000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.01109999999999994</v>
+        <v>-0.01110000000000005</v>
       </c>
       <c r="V12" t="n">
         <v>2.1657</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9278</v>
+        <v>5.519</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0211</v>
+        <v>5.4215</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.0975</v>
       </c>
       <c r="G13" t="n">
         <v>4.6189</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.2641</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7874</v>
+        <v>-0.387</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0679</v>
+        <v>0.1228</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>F. QUERO CARMONA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7844</v>
+        <v>3.4534</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5942</v>
+        <v>1.3903</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1902</v>
+        <v>2.0631</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9905</v>
+        <v>2.8095</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5891</v>
+        <v>1.244</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4015</v>
+        <v>1.5655</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1438</v>
+        <v>1.3701</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9814</v>
+        <v>0.7333</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1624</v>
+        <v>0.6368</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1533</v>
+        <v>1.4395</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3924</v>
+        <v>0.5108</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2391</v>
+        <v>0.9287</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5821</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1521</v>
+        <v>0.1663</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2146</v>
+        <v>0.1248</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9375</v>
+        <v>0.0415</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2239</v>
+        <v>1.8358</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1761</v>
+        <v>1.8358</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. QUERO CARMONA</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5902</v>
+        <v>2.5808</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6906</v>
+        <v>2.8715</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8996</v>
+        <v>-0.2906</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8095</v>
+        <v>1.9295</v>
       </c>
       <c r="H15" t="n">
-        <v>1.244</v>
+        <v>0.4391</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5655</v>
+        <v>1.4904</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3701</v>
+        <v>2.3374</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7333</v>
+        <v>1.0916</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6368</v>
+        <v>1.2458</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4395</v>
+        <v>-0.4079</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5108</v>
+        <v>-0.6525</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9287</v>
+        <v>0.2447</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3582</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3031</v>
+        <v>0.0095</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4251</v>
+        <v>0.2804</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.122</v>
+        <v>-0.2708</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8358</v>
+        <v>1.2239</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8358</v>
+        <v>1.2239</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0441</v>
+        <v>2.3112</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4711</v>
+        <v>1.6933</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4269</v>
+        <v>0.6178</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9295</v>
+        <v>0.9905</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4391</v>
+        <v>0.5891</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4904</v>
+        <v>0.4015</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3374</v>
+        <v>2.1438</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0916</v>
+        <v>1.9814</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2458</v>
+        <v>0.1624</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4079</v>
+        <v>-1.1533</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6525</v>
+        <v>-1.3924</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2447</v>
+        <v>0.2391</v>
       </c>
       <c r="P16" t="n">
         <v>-0.5821</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5271</v>
+        <v>0.6788</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.12</v>
+        <v>0.3137</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4071</v>
+        <v>0.3651</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2239</v>
+        <v>1.1761</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.977</v>
+        <v>2.2049</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0273</v>
+        <v>2.9282</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0503</v>
+        <v>-0.7232</v>
       </c>
       <c r="G17" t="n">
         <v>1.1678</v>
@@ -1780,13 +1780,13 @@
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.443</v>
+        <v>-0.2151</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7268</v>
+        <v>0.1741</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.3892</v>
       </c>
       <c r="V17" t="n">
         <v>0.2821</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9052</v>
+        <v>0.9691</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.074</v>
+        <v>0.1262</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9791</v>
+        <v>0.8429</v>
       </c>
       <c r="G18" t="n">
         <v>2.5844</v>
@@ -1858,13 +1858,13 @@
         <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4553</v>
+        <v>-0.3914</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1503</v>
+        <v>0.014</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2239</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3474</v>
+        <v>0.4292</v>
       </c>
       <c r="E19" t="n">
         <v>0.7581</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4107</v>
+        <v>-0.329</v>
       </c>
       <c r="G19" t="n">
         <v>0.026</v>
@@ -1936,13 +1936,13 @@
         <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4547</v>
+        <v>-0.3729</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1891</v>
+        <v>-1.9616</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.163</v>
+        <v>0.0372</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0261</v>
+        <v>-1.9989</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4535</v>
@@ -2014,13 +2014,13 @@
         <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4058</v>
+        <v>-0.1783</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3623</v>
+        <v>-0.1621</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0435</v>
+        <v>-0.0162</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9418</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4893</v>
+        <v>-2.298</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1903</v>
+        <v>0.4906</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6796</v>
+        <v>-2.7886</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1704</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2308</v>
+        <v>-0.0395</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3634</v>
+        <v>-0.0631</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1326</v>
+        <v>0.0236</v>
       </c>
       <c r="V21" t="n">
         <v>-0.894</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0715</v>
+        <v>-4.745</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6377</v>
+        <v>-2.3384</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4339</v>
+        <v>-2.4066</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6965</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.013</v>
+        <v>0.3396</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0924</v>
+        <v>0.3917</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0794</v>
+        <v>-0.0521</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4477</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5358</v>
+        <v>-7.1726</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9389</v>
+        <v>-3.4394</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5969</v>
+        <v>-3.7332</v>
       </c>
       <c r="G23" t="n">
         <v>-5.137</v>
@@ -2248,13 +2248,13 @@
         <v>1.1642</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6011</v>
+        <v>-0.0356</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4867</v>
+        <v>-0.0138</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1144</v>
+        <v>-0.0219</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2904</v>
+        <v>1.290400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>9.939099999999998</v>
+        <v>9.9391</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.6488</v>
+        <v>-8.648800000000001</v>
       </c>
       <c r="G24" t="n">
         <v>6.669199999999999</v>
@@ -2302,7 +2302,7 @@
         <v>17.1763</v>
       </c>
       <c r="K24" t="n">
-        <v>6.220400000000001</v>
+        <v>6.220399999999999</v>
       </c>
       <c r="L24" t="n">
         <v>10.9559</v>
@@ -2323,16 +2323,16 @@
         <v>-12.6121</v>
       </c>
       <c r="R24" t="n">
-        <v>9.701700000000001</v>
+        <v>9.701699999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3027</v>
+        <v>-0.3027000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>0.01090000000000002</v>
+        <v>0.01089999999999994</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3136999999999999</v>
+        <v>-0.3139</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1656</v>
